--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and â€œp</t>
+          <t>L38: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and â€œg</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L24: isolated marker/symbol line :: e</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 3."</t>
+          <t>L36: isolated marker/symbol line :: 1.«</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,26 +654,22 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1.â€œ</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 24</t>
+          <t>L38: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 4."</t>
+          <t>L38: isolated marker/symbol line :: 2.«</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -705,22 +705,22 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 2.â€œ</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>L43: isolated marker/symbol line :: 1.“</t>
+        </is>
+      </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 5."</t>
+          <t>L40: isolated marker/symbol line :: 3."</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -756,18 +756,18 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3.â€œ</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L44: isolated marker/symbol line :: 24</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 6."</t>
+          <t>L41: isolated marker/symbol line :: 4."</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -803,18 +803,18 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>L45: isolated marker/symbol line :: 2.“</t>
+        </is>
+      </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 7."</t>
+          <t>L43: isolated marker/symbol line :: 5."</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -850,18 +850,18 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4.â€œ</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L46: isolated marker/symbol line :: 3.“</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L44: isolated marker/symbol line :: 6."</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -897,18 +897,18 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L47: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: isolated marker/symbol line :: 7."</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -944,16 +944,20 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5.â€œ</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L48: isolated marker/symbol line :: 4.“</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -973,7 +977,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -987,16 +991,20 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L49: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1021,7 +1029,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1030,15 +1038,15 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6.â€œ</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L50: isolated marker/symbol line :: 5.“</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1059,12 +1067,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1073,15 +1081,15 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.â€œ</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L51: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1120,7 +1128,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L52: isolated marker/symbol line :: 6.“</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1159,7 +1171,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L53: isolated marker/symbol line :: 7.“</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
